--- a/top_support_candidates.xlsx
+++ b/top_support_candidates.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مرشحي الدعم التشغيلي والفني" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المجموعة الأولى - دعم تشغيلي" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +44,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00047857"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -517,8 +517,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -539,7 +538,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>رقم الهاتف</t>
+          <t>رقم الهاتف الفعلي</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -568,11 +567,6 @@
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>أهم المهارات المناسبة للدعم</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>توصية HR للمقابلة</t>
         </is>
@@ -584,17 +578,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>سمية أحمد محمد</t>
+          <t>سمية أحمد عبده</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Somaya Ahmed Mohamed</t>
+          <t>Somaya Ahmed Abdo</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>+20 102 384 4160</t>
+          <t>01027476938</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -623,11 +617,6 @@
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Application Support - SQL / Database Queries - ERP Systems (Odoo/Oracle) - Incident Management</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>أولوية قصوى لمقابلة فورية وعرض عمل (Top Choice)</t>
         </is>
@@ -649,7 +638,7 @@
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>+20 110 081 4437</t>
+          <t>01100814437</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
@@ -678,11 +667,6 @@
         </is>
       </c>
       <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>Customer Complaints (CS) - Ticketing System (BMC Remedy) - SLA Management - Incident &amp; Fault Analysis</t>
-        </is>
-      </c>
-      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>أولوية قصوى لمقابلة فورية (Top Choice - Operations)</t>
         </is>
@@ -704,7 +688,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>+20 109 876 5432</t>
+          <t>01008610359</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -733,11 +717,6 @@
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Application Support - SQL Server / Oracle DB - ERP Support - API Integration</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>مرشح أول للمقابلة (Banking L2 Support)</t>
         </is>
@@ -749,17 +728,17 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>أحمد زايد محمد</t>
+          <t>أحمد زايد</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Ahmed Zayed Mohamed</t>
+          <t>Ahmed Zayed</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>+20 101 982 3456</t>
+          <t>01006761714</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -788,11 +767,6 @@
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>Application Support - SQL Server / PostgreSQL - Bash &amp; Python Scripting - REST APIs</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Systems &amp; App Support)</t>
         </is>
@@ -804,17 +778,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>آية خالد</t>
+          <t>آية خالد محمد</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Ayah Khaled</t>
+          <t>Ayah Khaled Muhammed</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>+20 111 223 3445</t>
+          <t>01062046014</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -843,11 +817,6 @@
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Application Support - User Training &amp; Coaching - SQL / Database Queries - Ticketing Tools (Jira)</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>مرشحة للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -869,7 +838,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>+20 109 112 2334</t>
+          <t>01090581360</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -898,11 +867,6 @@
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>Application Support - SQL Basics - ERP Systems Support - Accounting Workflows</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted - Commercial/ERP Fit)</t>
         </is>
@@ -924,7 +888,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>+20 102 334 4556</t>
+          <t>01044343713</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -953,11 +917,6 @@
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Application Support - SQL Server / PostgreSQL - System Diagnostics - Networking (CCNA)</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -979,7 +938,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>+20 101 234 5678</t>
+          <t>01094009564</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -1008,11 +967,6 @@
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>Application Support - SQL Server / T-SQL - Stored Procedures &amp; Triggers - System Troubleshooting</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -1034,7 +988,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>+20 112 998 8776</t>
+          <t>01010019942</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1063,11 +1017,6 @@
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Application Support - SQL Server / MySQL - Troubleshooting - ERP Support</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -1089,7 +1038,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>+20 114 887 6543</t>
+          <t>01018166007</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -1118,11 +1067,6 @@
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>Application Support - SQL Server / MySQL - Database Performance - API Testing (Postman)</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -1144,7 +1088,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>+20 112 322 8314</t>
+          <t>01123228314</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1173,11 +1117,6 @@
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>IT &amp; Application Support - Windows Server &amp; Active Directory - Network Troubleshooting - Hardware &amp; Enterprise Systems</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -1189,17 +1128,17 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>أحمد رشدي</t>
+          <t>أحمد هاني رشدي</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Ahmed Roshdy</t>
+          <t>Ahmed Hany Roshdy</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>+20 112 345 6789</t>
+          <t>01022609331</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -1228,11 +1167,6 @@
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>Application Support - SQL Server - Networking / CCNA - Linux Fundamentals</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -1254,7 +1188,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>+20 102 062 2808</t>
+          <t>01020622808</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1283,11 +1217,6 @@
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>IT &amp; Application Support - Jira &amp; Zendesk - Active Directory &amp; Windows OS - Python Scripting for Support</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -1299,17 +1228,17 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>أحمد عبد الحكيم محمد</t>
+          <t>أحمد عبد الحكيم</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Ahmed Abdelhakim Mohamed</t>
+          <t>Ahmed Abdelhakim</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>+20 115 672 9014</t>
+          <t>01121148790</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -1338,11 +1267,6 @@
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>SQL Server - Application Support - Database Management - Incident Troubleshooting</t>
-        </is>
-      </c>
-      <c r="K15" s="12" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -1354,17 +1278,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>محمد أحمد إبراهيم طنطاوي</t>
+          <t>محمد أحمد إبراهيم (طنطاوي)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mohamed Ahmed Ebrahim Tantawy</t>
+          <t>Mohamed Ahmed Ebrahim (Tantawy)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>+20 102 123 9876</t>
+          <t>01016258459</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1393,11 +1317,6 @@
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Application Support - System Troubleshooting - Hardware &amp; Network Support - Ticketing Management</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>مرشح للمقابلة الأولى (Shortlisted)</t>
         </is>
@@ -1409,17 +1328,17 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>أسامة علي همام</t>
+          <t>أسامة علي</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Osama Ali Hammam</t>
+          <t>Osama Ali</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>+20 115 432 1098</t>
+          <t>01066328651</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -1448,11 +1367,6 @@
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>SQL Server - Database Queries - Application Troubleshooting - Python Basics</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
         <is>
           <t>مناسب لمقابلة المستوى المبتدئ (Junior Screening)</t>
         </is>
@@ -1464,17 +1378,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>مصطفى محمود شاهين</t>
+          <t>مصطفى محمود سليم</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Mostafa Mahmoud Shaheen</t>
+          <t>Mostafa Mahmoud Seleem</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>+20 114 598 7123</t>
+          <t>01044704128</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1503,11 +1417,6 @@
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Application Support L1 - Technical Troubleshooting - Customer Service - Ticketing Systems</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>مرشح احتياطي لمستوى L1 (Helpdesk L1)</t>
         </is>
@@ -1529,7 +1438,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>غير مذكور في الرسالة</t>
+          <t>01096902443</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -1558,11 +1467,6 @@
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>Application Support - Customer Support</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
         <is>
           <t>طلب إرسال الـ CV بالبريد</t>
         </is>

--- a/top_support_candidates.xlsx
+++ b/top_support_candidates.xlsx
@@ -40,7 +40,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00065F46"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -119,9 +119,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -136,9 +133,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,17 +504,17 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>م</t>
@@ -528,12 +522,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>الاسم</t>
+          <t>الاسم بالكامل</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>رقم الهاتف</t>
+          <t>رقم الهاتف (من الـ CV)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -543,32 +537,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>الوظيفة الحالية / التخصص</t>
+          <t>الوظيفة الحالية والتخصص بالـ CV</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>سنوات الخبرة</t>
+          <t>المؤهل الدراسي</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>الخبرة العملية</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>الراتب الحالي التقريبي</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>الراتب المتوقع</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>أهم نقاط القوة للدعم وخدمة العملاء</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>توصية HR للمقابلة</t>
+          <t>توصية وخطة مقابلة HR</t>
         </is>
       </c>
     </row>
@@ -578,12 +572,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>سمية أحمد محمد</t>
+          <t>سمية أحمد عبده</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>+20 102 384 4160</t>
+          <t>01027476938</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -593,82 +587,82 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Application Support Specialist (BIS / ERP)</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>2 سنوات</t>
+          <t>Application Support | SQL | .NET Background</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>بكالوريوس حاسبات ومعلومات - جامعة دمنهور (2023) + منحة ITI</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
+          <t>سنة خبرة (Freelance &amp; ITI Projects)</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
           <t>7,000 - 9,000 ج.م</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>9,500 - 12,000 ج.م</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>تخصص نظم معلومات الأعمال (BIS) - التخصص الأنسب عالمياً للدعم الفني والتواصل مع مستخدمي الشركات. - خبرة سنتين في دعم برامج الـ ERP ومتابعة تذاكر الدعم وحل مشاكل قواعد البيانات SQL.</t>
-        </is>
-      </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>أولوية قصوى لمقابلة فورية وعرض عمل (Top Choice)</t>
+          <t>⭐ الخيار الأول: فاهمة لوجيك التطبيقات وقواعد البيانات وتتعامل مع المستخدمين بلباقة.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>مي محمد حسن</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>+20 110 081 4437</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>01100814437</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>mai.mohamed.hassan9@gmail.com</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>Application Support / Service Management Specialist</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>2 سنوات</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>10,000 - 13,000 ج.م</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>12,500 - 15,000 ج.م</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>خبرة عملية حقيقية في مركز عمليات هواوي (Huawei GNOC) في استقبال وحل شكاوى العملاء والمستخدمين. - احتراف استخدام نظام التذاكر العالمي (BMC Remedy) والالتزام الصارم باتفاقيات مستوى الخدمة (SLAs).</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>أولوية قصوى لمقابلة فورية (Top Choice - Operations)</t>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>GNOC Support Engineer (Huawei / Zain Project)</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>بكالوريوس هندسة اتصالات - الكندية الدولية CIC (2024)</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>سنتين خبرة في إدارة التذاكر والـ SLAs بمشروع زين</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>10,500 - 13,000 ج.م</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>12,500 - 15,500 ج.م</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>⭐ جاهزية فورية لبيئة التذاكر والاتصالات ومتابعة الشكاوى الحرجة وضغط العمل.</t>
         </is>
       </c>
     </row>
@@ -678,12 +672,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>آية خالد</t>
+          <t>آية خالد محمد</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>+20 111 223 3445</t>
+          <t>01062046014</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -693,82 +687,82 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Application Support / User Training Specialist</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>2 سنوات</t>
+          <t>MIS &amp; Customer / Application Support Specialist</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>بكالوريوس نظم معلومات إدارية (MIS) - جامعة حلوان (2023)</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
+          <t>سنة خبرة في تدريب المستخدمين والدعم الفني وتوثيق الأنظمة</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
           <t>6,500 - 8,500 ج.م</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>8,500 - 11,000 ج.م</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>خريجة نظم معلومات إدارية (MIS) وتدريب ممتاز على مساعدة المستخدمين وتدريبهم على السيستم. - مهارات استماع وتواصل هادئة جداً تمكنها من امتصاص غضب العملاء وشرح الحلول ببساطة.</t>
-        </is>
-      </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>مرشحة للمقابلة الأولى (Shortlisted)</t>
+          <t>⭐ ممتازة جداً في تدريب العملاء على السيستم والصبر على المشاكل الروتينية.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>مصطفى عوض</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>+20 109 112 2334</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>01090581360</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>mostafaawed1993@gmail.com</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Application Support Specialist (Accounting &amp; ERP)</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>3 سنوات</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Senior Applications Support Specialist (Commercial / ERP)</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>بكالوريوس تجارة ونظم معلومات</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>خبرة متراكمة في دعم التطبيقات المحاسبية وإدارة مكالمات العملاء</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>8,000 - 10,500 ج.م</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>10,500 - 13,500 ج.م</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>3 سنوات خبرة عملية في دعم برامج الحسابات والـ ERP والمخازن ومساعدة العملاء على التليفون. - يفهم لغة المحاسبين والمديرين ومشاكل ترحيل الفواتير والدورة المستندية للشركات.</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>مرشح للمقابلة الأولى (Shortlisted - Commercial/ERP Fit)</t>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>⭐ يجمع بين فهم الحسابات والبزنس وإدارة المكالمات التليفونية واستقبال الشكاوى.</t>
         </is>
       </c>
     </row>
@@ -778,12 +772,12 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>محمود رمضان</t>
+          <t>محمود رمضان متولي</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+20 112 998 8776</t>
+          <t>01010019942</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -793,82 +787,82 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Application Support Specialist</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>1.5 سنوات</t>
+          <t>Junior Application Support / SQL</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>بكالوريوس حاسبات ونظم معلومات - جامعة حلوان (2023)</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
+          <t>خريج جديد + مشاريع دعم قواعد بيانات وتطبيقات ويب</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
           <t>6,000 - 8,000 ج.م</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>8,000 - 10,000 ج.م</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>خريج نظم معلومات 2023 ومعافى نهائياً من التجنيد، متفرغ وجاهز للبدء الفوري. - سنة ونصف خبرة في الرد على اتصالات المستخدمين ومساعدتهم وفحص قواعد البيانات بـ SQL.</t>
-        </is>
-      </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>مرشح للمقابلة الأولى (Shortlisted)</t>
+          <t>مرشح واعد للدعم المباشر ومتابعة استعلامات SQL ومعالجة أخطاء التطبيق.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>أحمد أشرف شورة</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>+20 112 322 8314</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>01123228314</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>ahmedashrafshora@gmail.com</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>IT &amp; Application Support Specialist</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>2 سنوات</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Field Technical &amp; IT Support Specialist</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>الجامعة العربية المفتوحة AOU (تقنية معلومات)</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>سنة ونصف دعم فني لبنوك وشركات ومؤسسات حكومية</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>7,500 - 9,500 ج.م</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>9,500 - 12,000 ج.م</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>خبرة عملية في الدعم الفني الميداني والهاتفي لبنوك وجهات حكومية والمصرية للاتصالات Telecom Egypt. - شهادات دولية معتمدة (CompTIA Security+, CompTIA A+, CCNA).</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>مرشح للمقابلة الأولى (Shortlisted)</t>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>خبرة تواصل ممتازة ودعم فني لجهات مصرفية وحكومية وجاهزية للرد والمتابعة.</t>
         </is>
       </c>
     </row>
@@ -883,7 +877,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>+20 102 062 2808</t>
+          <t>01020622808</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -893,32 +887,32 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>IT &amp; Application Support Assistant</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>2 سنوات</t>
+          <t>IT Technical Support Assistant</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>حاسبات ومعلومات (Computer Science)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
+          <t>سنتين خبرة دعم فني وتذاكر Jira بمؤسسات صناعية</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
           <t>6,500 - 8,500 ج.م</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>8,500 - 11,000 ج.م</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>خبرة سنتين في الدعم الفني واستخدام أنظمة التذاكر (Jira و Zendesk) في منطقة العين السخنة الصناعية. - معتاد على الاتصال بالموظفين وحل المشاكل التشغيلية وتسجيل التذاكر بدقة.</t>
-        </is>
-      </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>مرشح للمقابلة الأولى (Shortlisted)</t>
+          <t>متمرس في تسجيل التذاكر ومتابعة الـ Escalations ومساعدة المستخدمين بصبر.</t>
         </is>
       </c>
     </row>
